--- a/public/downloads/personal-budget-planner.xlsx
+++ b/public/downloads/personal-budget-planner.xlsx
@@ -251,7 +251,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0;(#,##0);-"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00;(#,##0.00);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);-"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
@@ -769,33 +769,28 @@
     <tabColor rgb="FF4A4A48"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="3" width="30" customWidth="1"/>
+    <col min="1" max="1" width="104" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="25.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" ht="29.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -805,7 +800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" ht="42.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
@@ -815,7 +810,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" ht="42.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
@@ -825,7 +820,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" ht="42.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>9</v>
       </c>
@@ -835,7 +830,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" ht="42.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>11</v>
       </c>
@@ -845,7 +840,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" ht="29.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
@@ -855,7 +850,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" ht="42.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>15</v>
       </c>
